--- a/pc/public/excel_template/base/org.xlsx
+++ b/pc/public/excel_template/base/org.xlsx
@@ -48,13 +48,13 @@
     <t xml:space="preserve">&lt;%=comment.create_usr_id_lbl%&gt;&lt;%selectList.create_usr_id = data.findAllUsr.map((item) =&gt; item.lbl)%&gt;&lt;%_dataValidation_({ sqref: `${ _col }2:${ _col }${ _lastRow }`, formula1: `"${ selectList.create_usr_id.join(",") }"` })%&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;%=comment.create_time%&gt;</t>
+    <t xml:space="preserve">&lt;%=comment.create_time_lbl%&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;%=comment.update_usr_id_lbl%&gt;&lt;%selectList.update_usr_id = data.findAllUsr.map((item) =&gt; item.lbl)%&gt;&lt;%_dataValidation_({ sqref: `${ _col }2:${ _col }${ _lastRow }`, formula1: `"${ selectList.update_usr_id.join(",") }"` })%&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;%=comment.update_time%&gt;</t>
+    <t xml:space="preserve">&lt;%=comment.update_time_lbl%&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;%forRow model in data.findAllOrg%&gt;&lt;%=model.lbl%&gt;</t>
